--- a/workspace/MLB_K_Prop_Model_2026-07-10_late.xlsx
+++ b/workspace/MLB_K_Prop_Model_2026-07-10_late.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="+0;-0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +84,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -112,12 +116,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
         <bgColor rgb="00D9D9D9"/>
       </patternFill>
@@ -125,6 +123,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B6C2"/>
+        <bgColor rgb="00F4B6C2"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -192,21 +201,18 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,6 +220,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,26 +231,17 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -610,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M37"/>
+  <dimension ref="B2:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -684,7 +682,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -694,7 +692,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -704,7 +702,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -940,13 +938,13 @@
         <v>0.28</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>-0.04</v>
+        <v>0.96</v>
       </c>
       <c r="J22" s="11" t="n">
-        <v>0.24</v>
+        <v>1.24</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1246,9 +1244,9 @@
       <c r="J30" s="11" t="n">
         <v>-0.58</v>
       </c>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>Under</t>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>No call</t>
         </is>
       </c>
     </row>
@@ -1314,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>0.11</v>
+        <v>1.11</v>
       </c>
       <c r="J32" s="11" t="n">
-        <v>0.11</v>
+        <v>1.11</v>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
@@ -1331,88 +1329,50 @@
     <row r="33">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Robbie Ray</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>ARI @ LAD</t>
+          <t>COL @ SFG</t>
         </is>
       </c>
       <c r="D33" s="10" t="n">
-        <v>9.980545043367766</v>
+        <v>7.613115158778199</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>5.44</v>
+        <v>4.98</v>
       </c>
       <c r="F33" s="10" t="n">
-        <v>5.97</v>
+        <v>5.37</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>-1.06</v>
+        <v>-0.52</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="K33" s="15" t="inlineStr">
-        <is>
-          <t>Under</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>COL @ SFG</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>7.613115158778199</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="J34" s="11" t="n">
         <v>-0.13</v>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>No call</t>
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="35">
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>v4.0 NOTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>v4.0 NOTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>v4.0 projections use today's FG export (live cohort). Backtest reference numbers (MAE 1.69, R² 0.23, DirAcc 64.4%) were scored against a 5/29 FG snapshot. Shadow comparison measures v4.0 vs v3.5 on identical inputs; both use today's FG export, so the relative delta is methodologically clean. Flags MATCH backtest: book_line=None, apply_short_mixture=False, apply_calibration=False. BF picks STILL gated on v3.5 residuals.</t>
         </is>
@@ -1422,7 +1382,7 @@
   <mergeCells count="3">
     <mergeCell ref="B3:M3"/>
     <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B37:K37"/>
+    <mergeCell ref="B36:K36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1459,7 +1419,7 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Raw Pitcher Statistics — FanGraphs + Baseball Savant</t>
         </is>
@@ -1558,60 +1518,56 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Luinder Avila</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>KCR</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>KCR @ BAL</t>
         </is>
       </c>
-      <c r="F4" s="21" t="n">
+      <c r="F4" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="20" t="n">
         <v>51.2</v>
       </c>
-      <c r="H4" s="21" t="n">
+      <c r="H4" s="20" t="n">
         <v>8.187097177178028</v>
       </c>
-      <c r="I4" s="20" t="n"/>
-      <c r="J4" s="20" t="n"/>
-      <c r="K4" s="20" t="n"/>
-      <c r="L4" s="21" t="n">
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="19" t="n"/>
+      <c r="K4" s="19" t="n"/>
+      <c r="L4" s="20" t="n">
         <v>8.949011</v>
       </c>
-      <c r="M4" s="21" t="n">
+      <c r="M4" s="20" t="n">
         <v>26.53486</v>
       </c>
-      <c r="N4" s="21" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="O4" s="21" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="P4" s="21" t="n">
+      <c r="N4" s="19" t="n"/>
+      <c r="O4" s="19" t="n"/>
+      <c r="P4" s="20" t="n">
         <v>5.051613151875805</v>
       </c>
-      <c r="Q4" s="21" t="n">
-        <v>4.416759551720121</v>
-      </c>
-      <c r="R4" s="21" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="S4" s="20" t="inlineStr">
+      <c r="Q4" s="20" t="n">
+        <v>4.410533488945463</v>
+      </c>
+      <c r="R4" s="20" t="n">
+        <v>4.511737935987158</v>
+      </c>
+      <c r="S4" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
@@ -1656,20 +1612,16 @@
       <c r="M5" s="10" t="n">
         <v>25.42101</v>
       </c>
-      <c r="N5" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="O5" s="10" t="n">
-        <v>41.3</v>
-      </c>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
       <c r="P5" s="10" t="n">
         <v>3.375000221975933</v>
       </c>
       <c r="Q5" s="10" t="n">
-        <v>3.895847414336508</v>
+        <v>3.88962135156185</v>
       </c>
       <c r="R5" s="10" t="n">
-        <v>4.34</v>
+        <v>4.344327891210893</v>
       </c>
       <c r="S5" s="9" t="inlineStr">
         <is>
@@ -1716,20 +1668,16 @@
       <c r="M6" s="10" t="n">
         <v>28.625</v>
       </c>
-      <c r="N6" s="10" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O6" s="10" t="n">
-        <v>35.9</v>
-      </c>
+      <c r="N6" s="9" t="n"/>
+      <c r="O6" s="9" t="n"/>
       <c r="P6" s="10" t="n">
         <v>4.281553398058253</v>
       </c>
       <c r="Q6" s="10" t="n">
-        <v>4.673383352594469</v>
+        <v>4.66715728981981</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>3.67</v>
+        <v>3.670868688433501</v>
       </c>
       <c r="S6" s="9" t="inlineStr">
         <is>
@@ -1738,40 +1686,40 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Hunter Greene</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>CHC @ CIN</t>
         </is>
       </c>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="n"/>
-      <c r="O7" s="20" t="n"/>
-      <c r="P7" s="20" t="n"/>
-      <c r="Q7" s="20" t="n"/>
-      <c r="R7" s="20" t="n"/>
-      <c r="S7" s="20" t="inlineStr">
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="19" t="n"/>
+      <c r="L7" s="19" t="n"/>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="19" t="n"/>
+      <c r="Q7" s="19" t="n"/>
+      <c r="R7" s="19" t="n"/>
+      <c r="S7" s="19" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
@@ -1816,20 +1764,16 @@
       <c r="M8" s="10" t="n">
         <v>24.242424</v>
       </c>
-      <c r="N8" s="10" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="O8" s="10" t="n">
-        <v>44.2</v>
-      </c>
+      <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
       <c r="P8" s="10" t="n">
         <v>4.790322893802156</v>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>3.833695018418625</v>
+        <v>3.827468955643967</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>4.56</v>
+        <v>4.571847103450785</v>
       </c>
       <c r="S8" s="9" t="inlineStr">
         <is>
@@ -1876,20 +1820,16 @@
       <c r="M9" s="10" t="n">
         <v>25.548478</v>
       </c>
-      <c r="N9" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="O9" s="10" t="n">
-        <v>33.5</v>
-      </c>
+      <c r="N9" s="9" t="n"/>
+      <c r="O9" s="9" t="n"/>
       <c r="P9" s="10" t="n">
         <v>2.61</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>3.829985294342041</v>
+        <v>3.823759231567383</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>4.68</v>
+        <v>4.692818604422035</v>
       </c>
       <c r="S9" s="9" t="inlineStr">
         <is>
@@ -1936,20 +1876,16 @@
       <c r="M10" s="10" t="n">
         <v>26.68693</v>
       </c>
-      <c r="N10" s="10" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="O10" s="10" t="n">
-        <v>31.2</v>
-      </c>
+      <c r="N10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
       <c r="P10" s="10" t="n">
         <v>2.801886994119824</v>
       </c>
       <c r="Q10" s="10" t="n">
-        <v>3.101117368455713</v>
+        <v>3.094891305681054</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>3.22</v>
+        <v>3.220026008170043</v>
       </c>
       <c r="S10" s="9" t="inlineStr">
         <is>
@@ -1996,20 +1932,16 @@
       <c r="M11" s="10" t="n">
         <v>25.797729</v>
       </c>
-      <c r="N11" s="10" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="O11" s="10" t="n">
-        <v>34.8</v>
-      </c>
+      <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
       <c r="P11" s="10" t="n">
         <v>4.002695500102812</v>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>3.863920619613675</v>
+        <v>3.857694556839017</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>3.78</v>
+        <v>3.779944192000212</v>
       </c>
       <c r="S11" s="9" t="inlineStr">
         <is>
@@ -2056,20 +1988,16 @@
       <c r="M12" s="10" t="n">
         <v>27.44043</v>
       </c>
-      <c r="N12" s="10" t="n">
-        <v>23</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>38.7</v>
-      </c>
+      <c r="N12" s="9" t="n"/>
+      <c r="O12" s="9" t="n"/>
       <c r="P12" s="10" t="n">
         <v>2.609665501524787</v>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>3.610691627962086</v>
+        <v>3.604465565187428</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>3.7</v>
+        <v>3.691771192937412</v>
       </c>
       <c r="S12" s="9" t="inlineStr">
         <is>
@@ -2116,20 +2044,16 @@
       <c r="M13" s="10" t="n">
         <v>29.078014</v>
       </c>
-      <c r="N13" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="O13" s="10" t="n">
-        <v>33.5</v>
-      </c>
+      <c r="N13" s="9" t="n"/>
+      <c r="O13" s="9" t="n"/>
       <c r="P13" s="10" t="n">
         <v>3.730263345129281</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>3.524590577808445</v>
+        <v>3.518364515033787</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>3.41</v>
+        <v>3.414250167583432</v>
       </c>
       <c r="S13" s="9" t="inlineStr">
         <is>
@@ -2176,20 +2100,16 @@
       <c r="M14" s="10" t="n">
         <v>24.088292</v>
       </c>
-      <c r="N14" s="10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="O14" s="10" t="n">
-        <v>31.4</v>
-      </c>
+      <c r="N14" s="9" t="n"/>
+      <c r="O14" s="9" t="n"/>
       <c r="P14" s="10" t="n">
         <v>7.04347834431285</v>
       </c>
       <c r="Q14" s="10" t="n">
-        <v>6.119985329882699</v>
+        <v>6.113759267108041</v>
       </c>
       <c r="R14" s="10" t="n">
-        <v>4.05</v>
+        <v>4.003184842344713</v>
       </c>
       <c r="S14" s="9" t="inlineStr">
         <is>
@@ -2236,20 +2156,16 @@
       <c r="M15" s="10" t="n">
         <v>29.236499</v>
       </c>
-      <c r="N15" s="10" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="O15" s="10" t="n">
-        <v>35.9</v>
-      </c>
+      <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
       <c r="P15" s="10" t="n">
         <v>3.55743252412519</v>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>3.738228553520493</v>
+        <v>3.732002490745835</v>
       </c>
       <c r="R15" s="10" t="n">
-        <v>3.72</v>
+        <v>3.737201255462713</v>
       </c>
       <c r="S15" s="9" t="inlineStr">
         <is>
@@ -2258,180 +2174,168 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Hunter Brown</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>HOU @ TEX</t>
         </is>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="20" t="n">
         <v>29.1</v>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="H16" s="20" t="n">
         <v>10.73863682914373</v>
       </c>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
-      <c r="K16" s="20" t="n"/>
-      <c r="L16" s="21" t="n">
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="20" t="n">
         <v>9.594096</v>
       </c>
-      <c r="M16" s="21" t="n">
+      <c r="M16" s="20" t="n">
         <v>28.413284</v>
       </c>
-      <c r="N16" s="21" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="O16" s="21" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="P16" s="21" t="n">
+      <c r="N16" s="19" t="n"/>
+      <c r="O16" s="19" t="n"/>
+      <c r="P16" s="20" t="n">
         <v>3.375000146302316</v>
       </c>
-      <c r="Q16" s="21" t="n">
-        <v>4.449530806521741</v>
-      </c>
-      <c r="R16" s="21" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="S16" s="20" t="inlineStr">
+      <c r="Q16" s="20" t="n">
+        <v>4.443304743747083</v>
+      </c>
+      <c r="R16" s="20" t="n">
+        <v>3.417877234554329</v>
+      </c>
+      <c r="S16" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Cal Quantrill</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>HOU @ TEX</t>
         </is>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="20" t="n">
         <v>40.1</v>
       </c>
-      <c r="H17" s="21" t="n">
+      <c r="H17" s="20" t="n">
         <v>6.024793863280262</v>
       </c>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="20" t="n"/>
-      <c r="L17" s="21" t="n">
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="20" t="n">
         <v>7.963247</v>
       </c>
-      <c r="M17" s="21" t="n">
+      <c r="M17" s="20" t="n">
         <v>24.808576</v>
       </c>
-      <c r="N17" s="21" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="O17" s="21" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="P17" s="21" t="n">
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="20" t="n">
         <v>3.347107701822368</v>
       </c>
-      <c r="Q17" s="21" t="n">
-        <v>4.657175498141943</v>
-      </c>
-      <c r="R17" s="21" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="S17" s="20" t="inlineStr">
+      <c r="Q17" s="20" t="n">
+        <v>4.650949435367285</v>
+      </c>
+      <c r="R17" s="20" t="n">
+        <v>4.869744695955387</v>
+      </c>
+      <c r="S17" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Grayson Rodriguez</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>LAA @ MIN</t>
         </is>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="F18" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="20" t="n">
         <v>25.2</v>
       </c>
-      <c r="H18" s="21" t="n">
+      <c r="H18" s="20" t="n">
         <v>8.415585249426234</v>
       </c>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="20" t="n"/>
-      <c r="L18" s="21" t="n">
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="20" t="n">
         <v>8.282828</v>
       </c>
-      <c r="M18" s="21" t="n">
+      <c r="M18" s="20" t="n">
         <v>25.050505</v>
       </c>
-      <c r="N18" s="21" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="O18" s="21" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="P18" s="21" t="n">
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="20" t="n">
         <v>8.064935864033474</v>
       </c>
-      <c r="Q18" s="21" t="n">
-        <v>5.145959521055764</v>
-      </c>
-      <c r="R18" s="21" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="S18" s="20" t="inlineStr">
+      <c r="Q18" s="20" t="n">
+        <v>5.139733458281106</v>
+      </c>
+      <c r="R18" s="20" t="n">
+        <v>7.220012644670943</v>
+      </c>
+      <c r="S18" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
@@ -2476,20 +2380,16 @@
       <c r="M19" s="10" t="n">
         <v>27.470141</v>
       </c>
-      <c r="N19" s="10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="O19" s="10" t="n">
-        <v>39.9</v>
-      </c>
+      <c r="N19" s="9" t="n"/>
+      <c r="O19" s="9" t="n"/>
       <c r="P19" s="10" t="n">
         <v>4.426229508196721</v>
       </c>
       <c r="Q19" s="10" t="n">
-        <v>5.103591851719091</v>
+        <v>5.097365788944432</v>
       </c>
       <c r="R19" s="10" t="n">
-        <v>4.46</v>
+        <v>4.48368584207049</v>
       </c>
       <c r="S19" s="9" t="inlineStr">
         <is>
@@ -2536,20 +2436,16 @@
       <c r="M20" s="10" t="n">
         <v>30.848995</v>
       </c>
-      <c r="N20" s="10" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O20" s="10" t="n">
-        <v>31.5</v>
-      </c>
+      <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
       <c r="P20" s="10" t="n">
         <v>2.273684210526316</v>
       </c>
       <c r="Q20" s="10" t="n">
-        <v>2.898932662763094</v>
+        <v>2.892706599988436</v>
       </c>
       <c r="R20" s="10" t="n">
-        <v>3.44</v>
+        <v>3.466871167079166</v>
       </c>
       <c r="S20" s="9" t="inlineStr">
         <is>
@@ -2596,20 +2492,16 @@
       <c r="M21" s="10" t="n">
         <v>25.366876</v>
       </c>
-      <c r="N21" s="10" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>51</v>
-      </c>
+      <c r="N21" s="9" t="n"/>
+      <c r="O21" s="9" t="n"/>
       <c r="P21" s="10" t="n">
         <v>3.857143084383524</v>
       </c>
       <c r="Q21" s="10" t="n">
-        <v>4.1045413369024</v>
+        <v>4.098315274127741</v>
       </c>
       <c r="R21" s="10" t="n">
-        <v>5.56</v>
+        <v>5.55685525557815</v>
       </c>
       <c r="S21" s="9" t="inlineStr">
         <is>
@@ -2618,80 +2510,80 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Shane Bieber</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>TOR @ SDP</t>
         </is>
       </c>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="20" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="20" t="n"/>
-      <c r="L22" s="20" t="n"/>
-      <c r="M22" s="20" t="n"/>
-      <c r="N22" s="20" t="n"/>
-      <c r="O22" s="20" t="n"/>
-      <c r="P22" s="20" t="n"/>
-      <c r="Q22" s="20" t="n"/>
-      <c r="R22" s="20" t="n"/>
-      <c r="S22" s="20" t="inlineStr">
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="19" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="n"/>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="19" t="n"/>
+      <c r="Q22" s="19" t="n"/>
+      <c r="R22" s="19" t="n"/>
+      <c r="S22" s="19" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>JP Sears</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>TOR @ SDP</t>
         </is>
       </c>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="20" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="20" t="n"/>
-      <c r="L23" s="20" t="n"/>
-      <c r="M23" s="20" t="n"/>
-      <c r="N23" s="20" t="n"/>
-      <c r="O23" s="20" t="n"/>
-      <c r="P23" s="20" t="n"/>
-      <c r="Q23" s="20" t="n"/>
-      <c r="R23" s="20" t="n"/>
-      <c r="S23" s="20" t="inlineStr">
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="19" t="n"/>
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="19" t="n"/>
+      <c r="O23" s="19" t="n"/>
+      <c r="P23" s="19" t="n"/>
+      <c r="Q23" s="19" t="n"/>
+      <c r="R23" s="19" t="n"/>
+      <c r="S23" s="19" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
@@ -2736,20 +2628,16 @@
       <c r="M24" s="10" t="n">
         <v>24.57378</v>
       </c>
-      <c r="N24" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="O24" s="10" t="n">
-        <v>38.9</v>
-      </c>
+      <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
       <c r="P24" s="10" t="n">
         <v>2.25</v>
       </c>
       <c r="Q24" s="10" t="n">
-        <v>4.00887418323093</v>
+        <v>4.002648120456271</v>
       </c>
       <c r="R24" s="10" t="n">
-        <v>5.01</v>
+        <v>4.997432661344337</v>
       </c>
       <c r="S24" s="9" t="inlineStr">
         <is>
@@ -2758,120 +2646,112 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Shohei Ohtani</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Kyle Hurt</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>ARI @ LAD</t>
         </is>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="H25" s="10" t="n">
-        <v>9.980545043367766</v>
-      </c>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="10" t="n">
-        <v>13.483146</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v>30.561798</v>
-      </c>
-      <c r="N25" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="O25" s="10" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="P25" s="10" t="n">
-        <v>1.785992270918442</v>
-      </c>
-      <c r="Q25" s="10" t="n">
-        <v>2.629712906246783</v>
-      </c>
-      <c r="R25" s="10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
+      <c r="F25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="20" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>11.22472006334627</v>
+      </c>
+      <c r="I25" s="19" t="n"/>
+      <c r="J25" s="19" t="n"/>
+      <c r="K25" s="19" t="n"/>
+      <c r="L25" s="20" t="n">
+        <v>16.778523</v>
+      </c>
+      <c r="M25" s="20" t="n">
+        <v>31.767338</v>
+      </c>
+      <c r="N25" s="19" t="n"/>
+      <c r="O25" s="19" t="n"/>
+      <c r="P25" s="20" t="n">
+        <v>4.550562187843082</v>
+      </c>
+      <c r="Q25" s="20" t="n">
+        <v>3.551961516322643</v>
+      </c>
+      <c r="R25" s="20" t="n">
+        <v>3.308761879210063</v>
+      </c>
+      <c r="S25" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Tanner Gordon</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>COL @ SFG</t>
         </is>
       </c>
-      <c r="F26" s="21" t="n">
+      <c r="F26" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="20" t="n">
         <v>45.1</v>
       </c>
-      <c r="H26" s="21" t="n">
+      <c r="H26" s="20" t="n">
         <v>9.13235319733208</v>
       </c>
-      <c r="I26" s="20" t="n"/>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="20" t="n"/>
-      <c r="L26" s="21" t="n">
+      <c r="I26" s="19" t="n"/>
+      <c r="J26" s="19" t="n"/>
+      <c r="K26" s="19" t="n"/>
+      <c r="L26" s="20" t="n">
         <v>10.657895</v>
       </c>
-      <c r="M26" s="21" t="n">
+      <c r="M26" s="20" t="n">
         <v>25.526316</v>
       </c>
-      <c r="N26" s="21" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="O26" s="21" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="P26" s="21" t="n">
+      <c r="N26" s="19" t="n"/>
+      <c r="O26" s="19" t="n"/>
+      <c r="P26" s="20" t="n">
         <v>6.948529606665712</v>
       </c>
-      <c r="Q26" s="21" t="n">
-        <v>5.039102995230667</v>
-      </c>
-      <c r="R26" s="21" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="S26" s="20" t="inlineStr">
+      <c r="Q26" s="20" t="n">
+        <v>5.032876932456008</v>
+      </c>
+      <c r="R26" s="20" t="n">
+        <v>4.874531559657108</v>
+      </c>
+      <c r="S26" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
@@ -2916,20 +2796,16 @@
       <c r="M27" s="10" t="n">
         <v>23.464014</v>
       </c>
-      <c r="N27" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="O27" s="10" t="n">
-        <v>37.6</v>
-      </c>
+      <c r="N27" s="9" t="n"/>
+      <c r="O27" s="9" t="n"/>
       <c r="P27" s="10" t="n">
         <v>3.452459199911044</v>
       </c>
       <c r="Q27" s="10" t="n">
-        <v>4.703591935896679</v>
+        <v>4.69736587312202</v>
       </c>
       <c r="R27" s="10" t="n">
-        <v>4.56</v>
+        <v>4.54970139587002</v>
       </c>
       <c r="S27" s="9" t="inlineStr">
         <is>
@@ -2968,24 +2844,24 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Classification &amp; Multipliers</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>Multiplier</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2997,7 +2873,7 @@
           <t>SwStr-Dominant</t>
         </is>
       </c>
-      <c r="C4" s="23" t="n">
+      <c r="C4" s="22" t="n">
         <v>0.95</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -3012,7 +2888,7 @@
           <t>Above-Zone</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n">
+      <c r="C5" s="22" t="n">
         <v>0.93</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -3027,7 +2903,7 @@
           <t>Below-Zone</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n">
+      <c r="C6" s="22" t="n">
         <v>0.92</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -3042,7 +2918,7 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C7" s="22" t="n">
         <v>0.91</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -3057,7 +2933,7 @@
           <t>CS-Dependent</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="22" t="n">
         <v>0.9</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -3067,7 +2943,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>v3.5p columns are SHADOW only — BF gate is unchanged today. Compare via backtest after 7 days.</t>
         </is>
@@ -3126,838 +3002,804 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Luinder Avila</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="25" t="n">
         <v>8.949011</v>
       </c>
-      <c r="G12" s="26" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J12" s="25" t="inlineStr"/>
-      <c r="K12" s="25" t="inlineStr"/>
+      <c r="J12" s="24" t="inlineStr"/>
+      <c r="K12" s="24" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Brandon Young</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D13" s="25" t="inlineStr">
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="25" t="n">
         <v>10.505213</v>
       </c>
-      <c r="G13" s="26" t="n">
-        <v>23</v>
-      </c>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="G13" s="24" t="n"/>
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J13" s="25" t="inlineStr"/>
-      <c r="K13" s="25" t="inlineStr"/>
+      <c r="J13" s="24" t="inlineStr"/>
+      <c r="K13" s="24" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Shota Imanaga</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>SwStr%&gt;=11</t>
         </is>
       </c>
-      <c r="E14" s="26" t="n">
+      <c r="E14" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F14" s="26" t="n">
+      <c r="F14" s="25" t="n">
         <v>14.5</v>
       </c>
-      <c r="G14" s="26" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="H14" s="27" t="inlineStr">
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="26" t="inlineStr">
         <is>
           <t>SwStr-Dom-Established</t>
         </is>
       </c>
-      <c r="I14" s="26" t="n">
+      <c r="I14" s="25" t="n">
         <v>0.92</v>
       </c>
-      <c r="J14" s="25" t="inlineStr"/>
-      <c r="K14" s="25" t="inlineStr"/>
+      <c r="J14" s="24" t="inlineStr"/>
+      <c r="K14" s="24" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Hunter Greene</t>
         </is>
       </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>Default (not in FG)</t>
         </is>
       </c>
-      <c r="E15" s="26" t="n">
+      <c r="E15" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="inlineStr"/>
-      <c r="K15" s="25" t="inlineStr"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="inlineStr"/>
+      <c r="K15" s="24" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Luis Castillo</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>SwStr%&gt;=11</t>
         </is>
       </c>
-      <c r="E16" s="26" t="n">
+      <c r="E16" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F16" s="26" t="n">
+      <c r="F16" s="25" t="n">
         <v>11.111111</v>
       </c>
-      <c r="G16" s="26" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="H16" s="25" t="inlineStr">
+      <c r="G16" s="24" t="n"/>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I16" s="26" t="n">
+      <c r="I16" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J16" s="25" t="inlineStr"/>
-      <c r="K16" s="25" t="inlineStr"/>
+      <c r="J16" s="24" t="inlineStr"/>
+      <c r="K16" s="24" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Nick Martinez</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="25" t="n">
         <v>8.351026000000001</v>
       </c>
-      <c r="G17" s="26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H17" s="25" t="inlineStr">
+      <c r="G17" s="24" t="n"/>
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I17" s="26" t="n">
+      <c r="I17" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J17" s="25" t="inlineStr"/>
-      <c r="K17" s="25" t="inlineStr"/>
+      <c r="J17" s="24" t="inlineStr"/>
+      <c r="K17" s="24" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Parker Messick</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>SwStr%&gt;=11</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="25" t="n">
         <v>11.306991</v>
       </c>
-      <c r="G18" s="26" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="G18" s="24" t="n"/>
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I18" s="26" t="n">
+      <c r="I18" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J18" s="25" t="inlineStr"/>
-      <c r="K18" s="25" t="inlineStr"/>
+      <c r="J18" s="24" t="inlineStr"/>
+      <c r="K18" s="24" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Sandy Alcantara</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="25" t="n">
         <v>10.005408</v>
       </c>
-      <c r="G19" s="26" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="H19" s="25" t="inlineStr">
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I19" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J19" s="25" t="inlineStr"/>
-      <c r="K19" s="25" t="inlineStr"/>
+      <c r="J19" s="24" t="inlineStr"/>
+      <c r="K19" s="24" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Sonny Gray</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F20" s="26" t="n">
+      <c r="F20" s="25" t="n">
         <v>10.146042</v>
       </c>
-      <c r="G20" s="26" t="n">
-        <v>23</v>
-      </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="G20" s="24" t="n"/>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I20" s="26" t="n">
+      <c r="I20" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J20" s="25" t="inlineStr"/>
-      <c r="K20" s="25" t="inlineStr"/>
+      <c r="J20" s="24" t="inlineStr"/>
+      <c r="K20" s="24" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" s="25" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Nolan McLean</t>
         </is>
       </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="25" t="n">
         <v>9.751773</v>
       </c>
-      <c r="G21" s="26" t="n">
-        <v>25</v>
-      </c>
-      <c r="H21" s="25" t="inlineStr">
+      <c r="G21" s="24" t="n"/>
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I21" s="26" t="n">
+      <c r="I21" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J21" s="25" t="inlineStr"/>
-      <c r="K21" s="25" t="inlineStr"/>
+      <c r="J21" s="24" t="inlineStr"/>
+      <c r="K21" s="24" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Jacob Lopez</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F22" s="26" t="n">
+      <c r="F22" s="25" t="n">
         <v>7.869482</v>
       </c>
-      <c r="G22" s="26" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I22" s="26" t="n">
+      <c r="I22" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J22" s="25" t="inlineStr"/>
-      <c r="K22" s="25" t="inlineStr"/>
+      <c r="J22" s="24" t="inlineStr"/>
+      <c r="K22" s="24" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Sean Burke</t>
         </is>
       </c>
-      <c r="C23" s="25" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D23" s="25" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F23" s="26" t="n">
+      <c r="F23" s="25" t="n">
         <v>10.552452</v>
       </c>
-      <c r="G23" s="26" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="H23" s="25" t="inlineStr">
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I23" s="26" t="n">
+      <c r="I23" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J23" s="25" t="inlineStr"/>
-      <c r="K23" s="25" t="inlineStr"/>
+      <c r="J23" s="24" t="inlineStr"/>
+      <c r="K23" s="24" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Hunter Brown</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F24" s="26" t="n">
+      <c r="F24" s="25" t="n">
         <v>9.594096</v>
       </c>
-      <c r="G24" s="26" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="H24" s="25" t="inlineStr">
+      <c r="G24" s="24" t="n"/>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I24" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J24" s="25" t="inlineStr"/>
-      <c r="K24" s="25" t="inlineStr"/>
+      <c r="J24" s="24" t="inlineStr"/>
+      <c r="K24" s="24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Cal Quantrill</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="25" t="n">
         <v>7.963247</v>
       </c>
-      <c r="G25" s="26" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J25" s="25" t="inlineStr"/>
-      <c r="K25" s="25" t="inlineStr"/>
+      <c r="J25" s="24" t="inlineStr"/>
+      <c r="K25" s="24" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Grayson Rodriguez</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F26" s="26" t="n">
+      <c r="F26" s="25" t="n">
         <v>8.282828</v>
       </c>
-      <c r="G26" s="26" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H26" s="25" t="inlineStr">
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I26" s="26" t="n">
+      <c r="I26" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J26" s="25" t="inlineStr"/>
-      <c r="K26" s="25" t="inlineStr"/>
+      <c r="J26" s="24" t="inlineStr"/>
+      <c r="K26" s="24" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Zebby Matthews</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="25" t="n">
         <v>9.989141999999999</v>
       </c>
-      <c r="G27" s="26" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="H27" s="25" t="inlineStr">
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I27" s="26" t="n">
+      <c r="I27" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J27" s="25" t="inlineStr"/>
-      <c r="K27" s="25" t="inlineStr"/>
+      <c r="J27" s="24" t="inlineStr"/>
+      <c r="K27" s="24" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Chris Sale</t>
         </is>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="24" t="inlineStr">
         <is>
           <t>SwStr%&gt;=11</t>
         </is>
       </c>
-      <c r="E28" s="26" t="n">
+      <c r="E28" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="25" t="n">
         <v>13.350616</v>
       </c>
-      <c r="G28" s="26" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="H28" s="25" t="inlineStr">
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I28" s="26" t="n">
+      <c r="I28" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J28" s="25" t="inlineStr"/>
-      <c r="K28" s="25" t="inlineStr"/>
+      <c r="J28" s="24" t="inlineStr"/>
+      <c r="K28" s="24" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Kyle Leahy</t>
         </is>
       </c>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E29" s="26" t="n">
+      <c r="E29" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F29" s="26" t="n">
+      <c r="F29" s="25" t="n">
         <v>8.735149999999999</v>
       </c>
-      <c r="G29" s="26" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="H29" s="25" t="inlineStr">
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I29" s="26" t="n">
+      <c r="I29" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J29" s="25" t="inlineStr"/>
-      <c r="K29" s="25" t="inlineStr"/>
+      <c r="J29" s="24" t="inlineStr"/>
+      <c r="K29" s="24" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Shane Bieber</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="24" t="inlineStr">
         <is>
           <t>Default (not in FG)</t>
         </is>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="25" t="inlineStr"/>
-      <c r="K30" s="25" t="inlineStr"/>
+      <c r="F30" s="24" t="n"/>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="inlineStr"/>
+      <c r="K30" s="24" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>JP Sears</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>Default (not in FG)</t>
         </is>
       </c>
-      <c r="E31" s="26" t="n">
+      <c r="E31" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F31" s="25" t="n"/>
-      <c r="G31" s="25" t="n"/>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="25" t="n"/>
-      <c r="J31" s="25" t="inlineStr"/>
-      <c r="K31" s="25" t="inlineStr"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="24" t="n"/>
+      <c r="I31" s="24" t="n"/>
+      <c r="J31" s="24" t="inlineStr"/>
+      <c r="K31" s="24" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>Eduardo Rodriguez</t>
         </is>
       </c>
-      <c r="C32" s="25" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="25" t="n">
         <v>7.81893</v>
       </c>
-      <c r="G32" s="26" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H32" s="25" t="inlineStr">
+      <c r="G32" s="24" t="n"/>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I32" s="26" t="n">
+      <c r="I32" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J32" s="25" t="inlineStr"/>
-      <c r="K32" s="25" t="inlineStr"/>
+      <c r="J32" s="24" t="inlineStr"/>
+      <c r="K32" s="24" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>Shohei Ohtani</t>
-        </is>
-      </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>Kyle Hurt</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>SwStr%&gt;=11</t>
         </is>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="E33" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F33" s="26" t="n">
-        <v>13.483146</v>
-      </c>
-      <c r="G33" s="26" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="H33" s="25" t="inlineStr">
+      <c r="F33" s="25" t="n">
+        <v>16.778523</v>
+      </c>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="26" t="inlineStr">
+        <is>
+          <t>SwStr-Dom-Rising</t>
+        </is>
+      </c>
+      <c r="I33" s="25" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="J33" s="27" t="inlineStr">
+        <is>
+          <t>BLOCK</t>
+        </is>
+      </c>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>SwStr-Dom young arm (GS=0≤12): no Under price</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>Tanner Gordon</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I33" s="26" t="n">
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J33" s="25" t="inlineStr"/>
-      <c r="K33" s="25" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>Tanner Gordon</t>
-        </is>
-      </c>
-      <c r="C34" s="25" t="inlineStr">
+      <c r="F34" s="25" t="n">
+        <v>10.657895</v>
+      </c>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="I34" s="25" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="J34" s="24" t="inlineStr"/>
+      <c r="K34" s="24" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>Robbie Ray</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>Default</t>
         </is>
       </c>
-      <c r="E34" s="26" t="n">
+      <c r="E35" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="F34" s="26" t="n">
-        <v>10.657895</v>
-      </c>
-      <c r="G34" s="26" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="H34" s="25" t="inlineStr">
+      <c r="F35" s="25" t="n">
+        <v>10.708016</v>
+      </c>
+      <c r="G35" s="24" t="n"/>
+      <c r="H35" s="24" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="I34" s="26" t="n">
+      <c r="I35" s="25" t="n">
         <v>0.91</v>
       </c>
-      <c r="J34" s="25" t="inlineStr"/>
-      <c r="K34" s="25" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>Robbie Ray</t>
-        </is>
-      </c>
-      <c r="C35" s="25" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="D35" s="25" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E35" s="26" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F35" s="26" t="n">
-        <v>10.708016</v>
-      </c>
-      <c r="G35" s="26" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H35" s="25" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="I35" s="26" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J35" s="25" t="inlineStr"/>
-      <c r="K35" s="25" t="inlineStr"/>
+      <c r="J35" s="24" t="inlineStr"/>
+      <c r="K35" s="24" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3994,14 +3836,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Lines &amp; Movement — DraftKings + FanDuel (The Odds API)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Note: This is the 11 AM run — line movement vs late refresh will populate in the *_late workbook.</t>
         </is>
@@ -4089,25 +3931,25 @@
         <v>4.5</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>-139</v>
+        <v>-160</v>
       </c>
       <c r="G5" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>-148</v>
+        <v>-162</v>
       </c>
       <c r="J5" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="K5" s="29" t="n">
-        <v>-148</v>
+        <v>-162</v>
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
@@ -4115,7 +3957,7 @@
         </is>
       </c>
       <c r="M5" s="9" t="n">
-        <v>-139</v>
+        <v>-160</v>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
@@ -4138,25 +3980,25 @@
         <v>4.5</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>-101</v>
+        <v>-103</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>-126</v>
+        <v>-124</v>
       </c>
       <c r="G6" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>-104</v>
+        <v>110</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>-122</v>
+        <v>-140</v>
       </c>
       <c r="J6" s="28" t="n">
         <v>4.5</v>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>-122</v>
+      <c r="K6" s="29" t="n">
+        <v>-140</v>
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
@@ -4164,11 +4006,11 @@
         </is>
       </c>
       <c r="M6" s="9" t="n">
-        <v>-122</v>
+        <v>-124</v>
       </c>
       <c r="N6" s="9" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>DK</t>
         </is>
       </c>
     </row>
@@ -4187,10 +4029,10 @@
         <v>5.5</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>-109</v>
+        <v>-121</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>-117</v>
+        <v>-106</v>
       </c>
       <c r="G7" s="28" t="n">
         <v>5.5</v>
@@ -4205,19 +4047,19 @@
         <v>5.5</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>-111</v>
+        <v>-106</v>
       </c>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="M7" s="9" t="n">
-        <v>-111</v>
+        <v>-106</v>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>DK</t>
         </is>
       </c>
     </row>
@@ -4236,10 +4078,10 @@
         <v>6.5</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>-110</v>
+        <v>-107</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="G8" s="28" t="n">
         <v>6.5</v>
@@ -4254,7 +4096,7 @@
         <v>6.5</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="L8" s="9" t="inlineStr">
         <is>
@@ -4262,7 +4104,7 @@
         </is>
       </c>
       <c r="M8" s="9" t="n">
-        <v>-115</v>
+        <v>-120</v>
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
@@ -4285,25 +4127,25 @@
         <v>4.5</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>-110</v>
+        <v>132</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>-116</v>
+        <v>-170</v>
       </c>
       <c r="G9" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>-128</v>
+        <v>-154</v>
       </c>
       <c r="J9" s="28" t="n">
         <v>4.5</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <v>-116</v>
+      <c r="K9" s="29" t="n">
+        <v>-170</v>
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
@@ -4311,11 +4153,11 @@
         </is>
       </c>
       <c r="M9" s="9" t="n">
-        <v>-116</v>
+        <v>-154</v>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FD</t>
         </is>
       </c>
     </row>
@@ -4331,28 +4173,28 @@
         </is>
       </c>
       <c r="D10" s="28" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>110</v>
+        <v>-168</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>-140</v>
+        <v>131</v>
       </c>
       <c r="G10" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>-146</v>
+        <v>-166</v>
       </c>
       <c r="J10" s="28" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K10" s="29" t="n">
-        <v>-146</v>
+        <v>-166</v>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
@@ -4360,7 +4202,7 @@
         </is>
       </c>
       <c r="M10" s="9" t="n">
-        <v>-140</v>
+        <v>131</v>
       </c>
       <c r="N10" s="9" t="inlineStr">
         <is>
@@ -4383,25 +4225,25 @@
         <v>5.5</v>
       </c>
       <c r="E11" s="28" t="n">
-        <v>-106</v>
+        <v>101</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>-121</v>
+        <v>-129</v>
       </c>
       <c r="G11" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="H11" s="28" t="n">
-        <v>-113</v>
+        <v>-104</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>-113</v>
+        <v>-122</v>
       </c>
       <c r="J11" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>-113</v>
+        <v>-122</v>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
@@ -4409,7 +4251,7 @@
         </is>
       </c>
       <c r="M11" s="9" t="n">
-        <v>-113</v>
+        <v>-122</v>
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
@@ -4432,33 +4274,33 @@
         <v>5.5</v>
       </c>
       <c r="E12" s="28" t="n">
-        <v>-113</v>
+        <v>110</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>-113</v>
+        <v>-140</v>
       </c>
       <c r="G12" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="H12" s="28" t="n">
-        <v>-104</v>
+        <v>114</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>-122</v>
+        <v>-146</v>
       </c>
       <c r="J12" s="28" t="n">
         <v>5.5</v>
       </c>
-      <c r="K12" s="9" t="n">
-        <v>-113</v>
+      <c r="K12" s="29" t="n">
+        <v>-146</v>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FD</t>
         </is>
       </c>
       <c r="M12" s="9" t="n">
-        <v>-113</v>
+        <v>-140</v>
       </c>
       <c r="N12" s="9" t="inlineStr">
         <is>
@@ -4481,25 +4323,25 @@
         <v>5.5</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>-135</v>
+        <v>-129</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G13" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="H13" s="28" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="J13" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
@@ -4507,7 +4349,7 @@
         </is>
       </c>
       <c r="M13" s="9" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
@@ -4530,25 +4372,25 @@
         <v>6.5</v>
       </c>
       <c r="E14" s="28" t="n">
-        <v>-121</v>
+        <v>-117</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>-105</v>
+        <v>-109</v>
       </c>
       <c r="G14" s="28" t="n">
         <v>6.5</v>
       </c>
       <c r="H14" s="28" t="n">
-        <v>-130</v>
+        <v>-118</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>102</v>
+        <v>-108</v>
       </c>
       <c r="J14" s="28" t="n">
         <v>6.5</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>102</v>
+        <v>-108</v>
       </c>
       <c r="L14" s="9" t="inlineStr">
         <is>
@@ -4556,7 +4398,7 @@
         </is>
       </c>
       <c r="M14" s="9" t="n">
-        <v>102</v>
+        <v>-108</v>
       </c>
       <c r="N14" s="9" t="inlineStr">
         <is>
@@ -4602,25 +4444,25 @@
         <v>5.5</v>
       </c>
       <c r="E16" s="28" t="n">
-        <v>-152</v>
+        <v>-126</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>119</v>
+        <v>-101</v>
       </c>
       <c r="G16" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="H16" s="28" t="n">
-        <v>-142</v>
+        <v>-111</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>112</v>
+        <v>-115</v>
       </c>
       <c r="J16" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>119</v>
+        <v>-101</v>
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
@@ -4628,7 +4470,7 @@
         </is>
       </c>
       <c r="M16" s="9" t="n">
-        <v>119</v>
+        <v>-101</v>
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
@@ -4651,25 +4493,25 @@
         <v>5.5</v>
       </c>
       <c r="E17" s="28" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G17" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>-130</v>
+        <v>-142</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J17" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="L17" s="9" t="inlineStr">
         <is>
@@ -4677,7 +4519,7 @@
         </is>
       </c>
       <c r="M17" s="9" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
@@ -4697,13 +4539,13 @@
         </is>
       </c>
       <c r="D18" s="28" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="E18" s="28" t="n">
-        <v>137</v>
+        <v>-177</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>-176</v>
+        <v>138</v>
       </c>
       <c r="G18" s="28" t="n">
         <v>3.5</v>
@@ -4715,22 +4557,22 @@
         <v>-174</v>
       </c>
       <c r="J18" s="28" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="K18" s="29" t="n">
-        <v>-176</v>
+        <v>-174</v>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
+          <t>FD</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>138</v>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
           <t>DK</t>
-        </is>
-      </c>
-      <c r="M18" s="9" t="n">
-        <v>-174</v>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
-        <is>
-          <t>FD</t>
         </is>
       </c>
     </row>
@@ -4749,33 +4591,33 @@
         <v>4.5</v>
       </c>
       <c r="E19" s="28" t="n">
-        <v>-105</v>
+        <v>128</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>-122</v>
+        <v>-163</v>
       </c>
       <c r="G19" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>-130</v>
+        <v>124</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>102</v>
+        <v>-158</v>
       </c>
       <c r="J19" s="28" t="n">
         <v>4.5</v>
       </c>
-      <c r="K19" s="9" t="n">
-        <v>102</v>
+      <c r="K19" s="29" t="n">
+        <v>-163</v>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="M19" s="9" t="n">
-        <v>102</v>
+        <v>-158</v>
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
@@ -4798,10 +4640,10 @@
         <v>5.5</v>
       </c>
       <c r="E20" s="28" t="n">
-        <v>-105</v>
+        <v>100</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>-122</v>
+        <v>-128</v>
       </c>
       <c r="G20" s="28" t="n">
         <v>5.5</v>
@@ -4824,7 +4666,7 @@
         </is>
       </c>
       <c r="M20" s="9" t="n">
-        <v>-122</v>
+        <v>-128</v>
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
@@ -4847,37 +4689,37 @@
         <v>6.5</v>
       </c>
       <c r="E21" s="28" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>-163</v>
+        <v>-143</v>
       </c>
       <c r="G21" s="28" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="H21" s="28" t="n">
-        <v>-164</v>
+        <v>118</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>128</v>
+        <v>-150</v>
       </c>
       <c r="J21" s="28" t="n">
         <v>6.5</v>
       </c>
       <c r="K21" s="29" t="n">
-        <v>-163</v>
+        <v>-150</v>
       </c>
       <c r="L21" s="9" t="inlineStr">
         <is>
+          <t>FD</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>-143</v>
+      </c>
+      <c r="N21" s="9" t="inlineStr">
+        <is>
           <t>DK</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="N21" s="9" t="inlineStr">
-        <is>
-          <t>FD</t>
         </is>
       </c>
     </row>
@@ -4896,25 +4738,25 @@
         <v>3.5</v>
       </c>
       <c r="E22" s="28" t="n">
-        <v>-158</v>
+        <v>-155</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G22" s="28" t="n">
         <v>3.5</v>
       </c>
       <c r="H22" s="28" t="n">
-        <v>-146</v>
+        <v>-154</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="J22" s="28" t="n">
         <v>3.5</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
@@ -4922,7 +4764,7 @@
         </is>
       </c>
       <c r="M22" s="9" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
@@ -4945,25 +4787,25 @@
         <v>4.5</v>
       </c>
       <c r="E23" s="28" t="n">
-        <v>-106</v>
+        <v>127</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>-121</v>
+        <v>-163</v>
       </c>
       <c r="G23" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="H23" s="28" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>-128</v>
+        <v>-156</v>
       </c>
       <c r="J23" s="28" t="n">
         <v>4.5</v>
       </c>
-      <c r="K23" s="9" t="n">
-        <v>-121</v>
+      <c r="K23" s="29" t="n">
+        <v>-163</v>
       </c>
       <c r="L23" s="9" t="inlineStr">
         <is>
@@ -4971,11 +4813,11 @@
         </is>
       </c>
       <c r="M23" s="9" t="n">
-        <v>-121</v>
+        <v>-156</v>
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FD</t>
         </is>
       </c>
     </row>
@@ -4994,25 +4836,25 @@
         <v>3.5</v>
       </c>
       <c r="E24" s="28" t="n">
-        <v>-138</v>
+        <v>-140</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G24" s="28" t="n">
         <v>3.5</v>
       </c>
       <c r="H24" s="28" t="n">
-        <v>-120</v>
+        <v>-128</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="J24" s="28" t="n">
         <v>3.5</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="L24" s="9" t="inlineStr">
         <is>
@@ -5020,7 +4862,7 @@
         </is>
       </c>
       <c r="M24" s="9" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="N24" s="9" t="inlineStr">
         <is>
@@ -5040,47 +4882,47 @@
         </is>
       </c>
       <c r="D25" s="28" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="E25" s="28" t="n">
-        <v>122</v>
+        <v>-169</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>-156</v>
+        <v>132</v>
       </c>
       <c r="G25" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="H25" s="28" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>-148</v>
+        <v>-164</v>
       </c>
       <c r="J25" s="28" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="K25" s="29" t="n">
-        <v>-156</v>
+        <v>-164</v>
       </c>
       <c r="L25" s="9" t="inlineStr">
         <is>
+          <t>FD</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>132</v>
+      </c>
+      <c r="N25" s="9" t="inlineStr">
+        <is>
           <t>DK</t>
-        </is>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>-148</v>
-      </c>
-      <c r="N25" s="9" t="inlineStr">
-        <is>
-          <t>FD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Kyle Hurt</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -5088,43 +4930,17 @@
           <t>ARI @ LAD</t>
         </is>
       </c>
-      <c r="D26" s="28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E26" s="28" t="n">
-        <v>-104</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>-123</v>
-      </c>
-      <c r="G26" s="28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H26" s="28" t="n">
-        <v>118</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>-150</v>
-      </c>
-      <c r="J26" s="28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K26" s="29" t="n">
-        <v>-150</v>
-      </c>
-      <c r="L26" s="9" t="inlineStr">
-        <is>
-          <t>FD</t>
-        </is>
-      </c>
-      <c r="M26" s="9" t="n">
-        <v>-123</v>
-      </c>
-      <c r="N26" s="9" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="n"/>
+      <c r="M26" s="9" t="n"/>
+      <c r="N26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="9" t="inlineStr">
@@ -5141,25 +4957,25 @@
         <v>4.5</v>
       </c>
       <c r="E27" s="28" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>-164</v>
+        <v>-160</v>
       </c>
       <c r="G27" s="28" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="H27" s="28" t="n">
-        <v>-148</v>
+        <v>122</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>114</v>
+        <v>-156</v>
       </c>
       <c r="J27" s="28" t="n">
         <v>4.5</v>
       </c>
       <c r="K27" s="29" t="n">
-        <v>-164</v>
+        <v>-160</v>
       </c>
       <c r="L27" s="9" t="inlineStr">
         <is>
@@ -5167,7 +4983,7 @@
         </is>
       </c>
       <c r="M27" s="9" t="n">
-        <v>114</v>
+        <v>-156</v>
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
@@ -5193,22 +5009,22 @@
         <v>-102</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="G28" s="28" t="n">
         <v>5.5</v>
       </c>
       <c r="H28" s="28" t="n">
-        <v>-111</v>
+        <v>100</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>-115</v>
+        <v>-130</v>
       </c>
       <c r="J28" s="28" t="n">
         <v>5.5</v>
       </c>
-      <c r="K28" s="9" t="n">
-        <v>-115</v>
+      <c r="K28" s="29" t="n">
+        <v>-130</v>
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
@@ -5216,11 +5032,11 @@
         </is>
       </c>
       <c r="M28" s="9" t="n">
-        <v>-115</v>
+        <v>-124</v>
       </c>
       <c r="N28" s="9" t="inlineStr">
         <is>
-          <t>FD</t>
+          <t>DK</t>
         </is>
       </c>
     </row>
@@ -5255,14 +5071,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Weather, Park, and Opposing Lineup</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Park factor source: v3.6.2 (Z-Files 2026, as of 2026-05-29) — lineup-weighted by R/L/S handedness counts.</t>
         </is>
@@ -5344,14 +5160,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>86F, Partly Cloudy, Wind 5 mph, Out To RF</t>
+        </is>
+      </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J5" s="30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5383,14 +5203,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>86F, Partly Cloudy, Wind 5 mph, Out To RF</t>
+        </is>
+      </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J6" s="30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -5422,14 +5246,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>84F, Partly Cloudy, Wind 6 mph, Out To LF</t>
+        </is>
+      </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J7" s="30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -5461,14 +5289,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>84F, Partly Cloudy, Wind 6 mph, Out To LF</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J8" s="30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -5500,7 +5332,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>72F, Dome, Wind 0 mph, None</t>
+        </is>
+      </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -5539,7 +5375,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>72F, Dome, Wind 0 mph, None</t>
+        </is>
+      </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -5578,7 +5418,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>72F, Roof Closed, Wind 0 mph, None</t>
+        </is>
+      </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -5617,7 +5461,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>72F, Roof Closed, Wind 0 mph, None</t>
+        </is>
+      </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -5656,14 +5504,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>83F, Clear, Wind 10 mph, Out To RF</t>
+        </is>
+      </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J13" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -5695,14 +5547,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>83F, Clear, Wind 10 mph, Out To RF</t>
+        </is>
+      </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J14" s="30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -5734,7 +5590,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>75F, Partly Cloudy, Wind 11 mph, Out To RF</t>
+        </is>
+      </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -5773,7 +5633,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>75F, Partly Cloudy, Wind 11 mph, Out To RF</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -5812,7 +5676,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>72F, Roof Closed, Wind 0 mph, None</t>
+        </is>
+      </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -5851,7 +5719,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>72F, Roof Closed, Wind 0 mph, None</t>
+        </is>
+      </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -5890,14 +5762,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>86F, Partly Cloudy, Wind 5 mph, R To L</t>
+        </is>
+      </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J19" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -5929,14 +5805,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>86F, Partly Cloudy, Wind 5 mph, R To L</t>
+        </is>
+      </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J20" s="30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5968,14 +5848,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>88F, Overcast, Wind 3 mph, Out To CF</t>
+        </is>
+      </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
-      <c r="J21" s="30" t="n">
-        <v>27</v>
+      <c r="J21" s="31" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -6007,14 +5891,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>88F, Overcast, Wind 3 mph, Out To CF</t>
+        </is>
+      </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
-      <c r="J22" s="30" t="n">
-        <v>27</v>
+      <c r="J22" s="31" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="23">
@@ -6046,7 +5934,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>70F, Partly Cloudy, Wind 6 mph, Out To RF</t>
+        </is>
+      </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -6085,7 +5977,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>70F, Partly Cloudy, Wind 6 mph, Out To RF</t>
+        </is>
+      </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -6124,7 +6020,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>80F, Partly Cloudy, Wind 8 mph, Out To CF</t>
+        </is>
+      </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -6137,7 +6037,7 @@
     <row r="26">
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Kyle Hurt</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
@@ -6163,7 +6063,11 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>80F, Partly Cloudy, Wind 8 mph, Out To CF</t>
+        </is>
+      </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
@@ -6202,14 +6106,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>60F, Clear, Wind 13 mph, Out To LF</t>
+        </is>
+      </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J27" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -6241,14 +6149,18 @@
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="H28" s="8" t="inlineStr"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>60F, Clear, Wind 13 mph, Out To LF</t>
+        </is>
+      </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
           <t>Projected</t>
         </is>
       </c>
       <c r="J28" s="30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6288,14 +6200,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Model Run — v3.5 (production) + v4.0 SHADOW</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>v3.5 = (K/9 × IP/GS / 9) × Multiplier + env adj → v3.3 4-stage calibration. v4.0 = K/9 × projected_IP / 9 + same env → v3.3 cal. Both with v3.6.2 park factors.</t>
         </is>
@@ -6379,49 +6291,49 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Luinder Avila</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>KCR @ BAL</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>BAL</t>
         </is>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="32" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="20" t="n"/>
-      <c r="K5" s="20" t="n"/>
-      <c r="L5" s="32" t="n">
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="19" t="n"/>
+      <c r="L5" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="M5" s="20" t="n"/>
-      <c r="N5" s="20" t="n"/>
-      <c r="O5" s="20" t="inlineStr">
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="P5" s="19" t="inlineStr">
+      <c r="P5" s="18" t="inlineStr">
         <is>
           <t>GS=8 &lt; 10</t>
         </is>
@@ -6542,49 +6454,49 @@
       <c r="P7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Hunter Greene</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>CHC @ CIN</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="32" t="n">
         <v>0.067</v>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="32" t="n">
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="33" t="n">
         <v>6.5</v>
       </c>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="20" t="inlineStr">
+      <c r="M8" s="19" t="n"/>
+      <c r="N8" s="19" t="n"/>
+      <c r="O8" s="19" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="P8" s="19" t="inlineStr">
+      <c r="P8" s="18" t="inlineStr">
         <is>
           <t>Not in FG dashboard cohort</t>
         </is>
@@ -6689,13 +6601,13 @@
         <v>0.28</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>-0.04</v>
+        <v>0.96</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>0.24</v>
+        <v>1.24</v>
       </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
@@ -7041,147 +6953,147 @@
       <c r="P16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Hunter Brown</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>HOU @ TEX</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E17" s="31" t="n">
+      <c r="E17" s="32" t="n">
         <v>0.033</v>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H17" s="20" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="20" t="n"/>
-      <c r="L17" s="32" t="n">
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="33" t="n">
         <v>5.5</v>
       </c>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="n"/>
-      <c r="O17" s="20" t="inlineStr">
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="P17" s="19" t="inlineStr">
+      <c r="P17" s="18" t="inlineStr">
         <is>
           <t>GS=6 &lt; 10</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Cal Quantrill</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>HOU @ TEX</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="32" t="n">
         <v>0.033</v>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H18" s="20" t="n"/>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="20" t="n"/>
-      <c r="L18" s="32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M18" s="20" t="n"/>
-      <c r="N18" s="20" t="n"/>
-      <c r="O18" s="20" t="inlineStr">
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="P18" s="19" t="inlineStr">
+      <c r="P18" s="18" t="inlineStr">
         <is>
           <t>GS=3 &lt; 10</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Grayson Rodriguez</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>LAA @ MIN</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E19" s="31" t="n">
+      <c r="E19" s="32" t="n">
         <v>0.1</v>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="G19" s="20" t="inlineStr">
+      <c r="G19" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="32" t="n">
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="M19" s="20" t="n"/>
-      <c r="N19" s="20" t="n"/>
-      <c r="O19" s="20" t="inlineStr">
+      <c r="M19" s="19" t="n"/>
+      <c r="N19" s="19" t="n"/>
+      <c r="O19" s="19" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="P19" s="19" t="inlineStr">
+      <c r="P19" s="18" t="inlineStr">
         <is>
           <t>GS=6 &lt; 10</t>
         </is>
@@ -7359,98 +7271,98 @@
       <c r="P22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Shane Bieber</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>TOR @ SDP</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="E23" s="31" t="n">
+      <c r="E23" s="32" t="n">
         <v>0.067</v>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="G23" s="20" t="inlineStr">
+      <c r="G23" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H23" s="20" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="20" t="n"/>
-      <c r="L23" s="32" t="n">
+      <c r="H23" s="19" t="n"/>
+      <c r="I23" s="19" t="n"/>
+      <c r="J23" s="19" t="n"/>
+      <c r="K23" s="19" t="n"/>
+      <c r="L23" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="M23" s="20" t="n"/>
-      <c r="N23" s="20" t="n"/>
-      <c r="O23" s="20" t="inlineStr">
+      <c r="M23" s="19" t="n"/>
+      <c r="N23" s="19" t="n"/>
+      <c r="O23" s="19" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="P23" s="19" t="inlineStr">
+      <c r="P23" s="18" t="inlineStr">
         <is>
           <t>Not in FG dashboard cohort</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>JP Sears</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>TOR @ SDP</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="E24" s="31" t="n">
+      <c r="E24" s="32" t="n">
         <v>0.067</v>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>0R/0L/0S</t>
         </is>
       </c>
-      <c r="G24" s="20" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H24" s="20" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="20" t="n"/>
-      <c r="L24" s="32" t="n">
+      <c r="H24" s="19" t="n"/>
+      <c r="I24" s="19" t="n"/>
+      <c r="J24" s="19" t="n"/>
+      <c r="K24" s="19" t="n"/>
+      <c r="L24" s="33" t="n">
         <v>3.5</v>
       </c>
-      <c r="M24" s="20" t="n"/>
-      <c r="N24" s="20" t="n"/>
-      <c r="O24" s="20" t="inlineStr">
+      <c r="M24" s="19" t="n"/>
+      <c r="N24" s="19" t="n"/>
+      <c r="O24" s="19" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="P24" s="19" t="inlineStr">
+      <c r="P24" s="18" t="inlineStr">
         <is>
           <t>Not in FG dashboard cohort</t>
         </is>
@@ -7498,122 +7410,112 @@
         <v>0</v>
       </c>
       <c r="L25" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M25" s="11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N25" s="11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O25" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="P25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Kyle Hurt</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>0R/0L/0S</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="n"/>
+      <c r="I26" s="19" t="n"/>
+      <c r="J26" s="19" t="n"/>
+      <c r="K26" s="19" t="n"/>
+      <c r="L26" s="19" t="n"/>
+      <c r="M26" s="19" t="n"/>
+      <c r="N26" s="19" t="n"/>
+      <c r="O26" s="19" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="P26" s="18" t="inlineStr">
+        <is>
+          <t>GS=0 &lt; 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Tanner Gordon</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>COL @ SFG</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>SFG</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>0R/0L/0S</t>
+        </is>
+      </c>
+      <c r="G27" s="19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="n"/>
+      <c r="I27" s="19" t="n"/>
+      <c r="J27" s="19" t="n"/>
+      <c r="K27" s="19" t="n"/>
+      <c r="L27" s="33" t="n">
         <v>4.5</v>
       </c>
-      <c r="M25" s="11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="N25" s="11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="O25" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P25" s="8" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Shohei Ohtani</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>ARI @ LAD</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>0R/0L/0S</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="I26" s="10" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="J26" s="10" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="K26" s="13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" s="11" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="N26" s="11" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="O26" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="P26" s="8" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>Tanner Gordon</t>
-        </is>
-      </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>COL @ SFG</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>SFG</t>
-        </is>
-      </c>
-      <c r="E27" s="31" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>0R/0L/0S</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="20" t="n"/>
-      <c r="L27" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M27" s="20" t="n"/>
-      <c r="N27" s="20" t="n"/>
-      <c r="O27" s="20" t="inlineStr">
+      <c r="M27" s="19" t="n"/>
+      <c r="N27" s="19" t="n"/>
+      <c r="O27" s="19" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="P27" s="19" t="inlineStr">
+      <c r="P27" s="18" t="inlineStr">
         <is>
           <t>GS=4 &lt; 10</t>
         </is>
@@ -7691,7 +7593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O6"/>
+  <dimension ref="B2:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7712,14 +7614,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>BF Picks — v3.5 GATE (residual ≤ -0.75, best Under ≤ -130, Rule 5 pass, PPD ≤ 50%)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>BF gates remain on v3.5 during 7-day shadow period for v4.0.</t>
         </is>
@@ -7798,122 +7700,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="33" t="inlineStr">
-        <is>
-          <t>Chris Sale</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>ATL @ STL</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-10T20:15:00+00:00</t>
-        </is>
-      </c>
-      <c r="F5" s="34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>-163 (DK)</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>128 (FD)</t>
-        </is>
-      </c>
-      <c r="I5" s="35" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="J5" s="35" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="K5" s="36" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="L5" s="36" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="M5" s="37" t="n">
-        <v>27</v>
-      </c>
-      <c r="N5" s="15" t="inlineStr">
-        <is>
-          <t>Under</t>
-        </is>
-      </c>
-      <c r="O5" s="33" t="inlineStr">
-        <is>
-          <t>Gate PASS: residual -1.13 ≤ -0.75, qualifying Under -163 (DK), Rule 5 pass, PPD ≤ 50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>Shohei Ohtani</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>ARI @ LAD</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="inlineStr">
-        <is>
-          <t>2026-07-10T22:10:00+00:00</t>
-        </is>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>-150 (FD)</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="inlineStr">
-        <is>
-          <t>-123 (DK)</t>
-        </is>
-      </c>
-      <c r="I6" s="35" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="J6" s="35" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="K6" s="36" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="L6" s="36" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="M6" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="15" t="inlineStr">
-        <is>
-          <t>Under</t>
-        </is>
-      </c>
-      <c r="O6" s="33" t="inlineStr">
-        <is>
-          <t>Gate PASS: residual -1.06 ≤ -0.75, qualifying Under -150 (FD), Rule 5 pass, PPD ≤ 50%</t>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>No BF picks today.</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J11"/>
+  <dimension ref="B2:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -7948,7 +7737,7 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Watch List — Rule 5 fails, FG cohort misses, or non-priced starters</t>
         </is>
@@ -8002,310 +7791,351 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Luinder Avila</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>KCR</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D4" s="18" t="inlineStr">
         <is>
           <t>KCR @ BAL</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>2026-07-10T19:05:00+00:00</t>
         </is>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="20" t="n">
+      <c r="G4" s="19" t="n">
         <v>51.2</v>
       </c>
-      <c r="H4" s="21" t="n">
+      <c r="H4" s="20" t="n">
         <v>8.187097177178028</v>
       </c>
-      <c r="I4" s="20" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="J4" s="18" t="inlineStr">
         <is>
           <t>GS=8 &lt; 10</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>Hunter Greene</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>CIN</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>CHC @ CIN</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>2026-07-10T19:10:00+00:00</t>
         </is>
       </c>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="F5" s="19" t="n"/>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="J5" s="19" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>Not in FG dashboard cohort</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Hunter Brown</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>HOU</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>HOU @ TEX</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>2026-07-10T20:05:00+00:00</t>
         </is>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="19" t="n">
         <v>29.1</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="20" t="n">
         <v>10.73863682914373</v>
       </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
-      <c r="J6" s="19" t="inlineStr">
+      <c r="J6" s="18" t="inlineStr">
         <is>
           <t>GS=6 &lt; 10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Cal Quantrill</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>HOU @ TEX</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>2026-07-10T20:05:00+00:00</t>
         </is>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="19" t="n">
         <v>40.1</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="20" t="n">
         <v>6.024793863280262</v>
       </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>GS=3 &lt; 10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Grayson Rodriguez</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>LAA @ MIN</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>2026-07-10T20:10:00+00:00</t>
         </is>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="19" t="n">
         <v>25.2</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="20" t="n">
         <v>8.415585249426234</v>
       </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="18" t="inlineStr">
         <is>
           <t>GS=6 &lt; 10</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Shane Bieber</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>TOR</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>TOR @ SDP</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>2026-07-10T21:40:00+00:00</t>
         </is>
       </c>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>Not in FG dashboard cohort</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>JP Sears</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>SDP</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>TOR @ SDP</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>2026-07-10T21:40:00+00:00</t>
         </is>
       </c>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="J10" s="18" t="inlineStr">
         <is>
           <t>Not in FG dashboard cohort</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Kyle Hurt</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>ARI @ LAD</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>11.22472006334627</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>GS=0 &lt; 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Tanner Gordon</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>COL @ SFG</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>2026-07-10T22:15:00+00:00</t>
         </is>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G12" s="19" t="n">
         <v>45.1</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H12" s="20" t="n">
         <v>9.13235319733208</v>
       </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>dashboard</t>
         </is>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>GS=4 &lt; 10</t>
         </is>
